--- a/test/fixtures/Test_format_good_Seq.xlsx
+++ b/test/fixtures/Test_format_good_Seq.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jc2017/Documents/MyRepos/safedata_validator/test/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C156A4B2-17A1-5446-BD0D-05236AE23421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741A5BF2-874E-8247-BCAC-7B0C9340356C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1060" windowWidth="27860" windowHeight="15840" activeTab="6" xr2:uid="{819B57D8-7F20-471A-9405-EB60A28E68AA}"/>
+    <workbookView xWindow="0" yWindow="1060" windowWidth="27860" windowHeight="15840" activeTab="7" xr2:uid="{819B57D8-7F20-471A-9405-EB60A28E68AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="6" r:id="rId1"/>
     <sheet name="Locations" sheetId="7" r:id="rId2"/>
     <sheet name="GBIFTaxa" sheetId="8" r:id="rId3"/>
     <sheet name="SeqTaxa" sheetId="1" r:id="rId4"/>
-    <sheet name="DF" sheetId="9" r:id="rId5"/>
-    <sheet name="Incidence" sheetId="10" r:id="rId6"/>
-    <sheet name="MicrobeDF" sheetId="11" r:id="rId7"/>
+    <sheet name="MoreTaxa" sheetId="12" r:id="rId5"/>
+    <sheet name="DF" sheetId="9" r:id="rId6"/>
+    <sheet name="Incidence" sheetId="10" r:id="rId7"/>
+    <sheet name="MicrobeDF" sheetId="11" r:id="rId8"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8157" uniqueCount="1433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8319" uniqueCount="1458">
   <si>
     <t>Kingdom</t>
   </si>
@@ -4331,6 +4332,81 @@
   </si>
   <si>
     <t>g__Chloridium</t>
+  </si>
+  <si>
+    <t>Sequenced taxa sheet name</t>
+  </si>
+  <si>
+    <t>SeqTaxa</t>
+  </si>
+  <si>
+    <t>Reference database name</t>
+  </si>
+  <si>
+    <t>Greengenes</t>
+  </si>
+  <si>
+    <t>Reference database version</t>
+  </si>
+  <si>
+    <t>v1.7.9</t>
+  </si>
+  <si>
+    <t>Reference database link</t>
+  </si>
+  <si>
+    <t>https://greengenes2.ucsd.edu</t>
+  </si>
+  <si>
+    <t>MoreTaxa</t>
+  </si>
+  <si>
+    <t>SILVA</t>
+  </si>
+  <si>
+    <t>2025-03</t>
+  </si>
+  <si>
+    <t>ASV_119</t>
+  </si>
+  <si>
+    <t>ASV_120</t>
+  </si>
+  <si>
+    <t>ASV_121</t>
+  </si>
+  <si>
+    <t>ASV_122</t>
+  </si>
+  <si>
+    <t>ASV_123</t>
+  </si>
+  <si>
+    <t>ASV_124</t>
+  </si>
+  <si>
+    <t>ASV_125</t>
+  </si>
+  <si>
+    <t>ASV_126</t>
+  </si>
+  <si>
+    <t>ASV_127</t>
+  </si>
+  <si>
+    <t>ASV_128</t>
+  </si>
+  <si>
+    <t>ASV_129</t>
+  </si>
+  <si>
+    <t>ASV_130</t>
+  </si>
+  <si>
+    <t>ASV_131</t>
+  </si>
+  <si>
+    <t>ASV_132</t>
   </si>
 </sst>
 </file>
@@ -4718,11 +4794,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{915E50AF-1B61-0E4A-B651-AEECBCF18168}">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="54" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
     <col min="4" max="4" width="20.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -4994,9 +5070,51 @@
         <v>5.07</v>
       </c>
     </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1434</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1438</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>1440</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D8" r:id="rId1" xr:uid="{6D635858-507F-FB42-869F-7B19AB4CC72D}"/>
+    <hyperlink ref="B31" r:id="rId2" xr:uid="{0ADC1EA3-96B0-B242-A987-A66576FCBCD7}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6779,6 +6897,458 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAA9F945-EFC8-D343-A3F3-F80A0E67C36D}">
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1372</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F2" t="s">
+        <v>1374</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1375</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1376</v>
+      </c>
+      <c r="I2" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1381</v>
+      </c>
+      <c r="G3" t="s">
+        <v>1382</v>
+      </c>
+      <c r="H3" t="s">
+        <v>1383</v>
+      </c>
+      <c r="I3" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1372</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1386</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1387</v>
+      </c>
+      <c r="H4" t="s">
+        <v>1388</v>
+      </c>
+      <c r="I4" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1381</v>
+      </c>
+      <c r="G5" t="s">
+        <v>1382</v>
+      </c>
+      <c r="H5" t="s">
+        <v>1383</v>
+      </c>
+      <c r="I5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1393</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1394</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1395</v>
+      </c>
+      <c r="H6" t="s">
+        <v>1396</v>
+      </c>
+      <c r="I6" t="s">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1399</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1400</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1401</v>
+      </c>
+      <c r="H7" t="s">
+        <v>1402</v>
+      </c>
+      <c r="I7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1381</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1404</v>
+      </c>
+      <c r="H8" t="s">
+        <v>1405</v>
+      </c>
+      <c r="I8" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1381</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1382</v>
+      </c>
+      <c r="H9" t="s">
+        <v>1383</v>
+      </c>
+      <c r="I9" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1410</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1411</v>
+      </c>
+      <c r="G10" t="s">
+        <v>1412</v>
+      </c>
+      <c r="H10" t="s">
+        <v>1413</v>
+      </c>
+      <c r="I10" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1381</v>
+      </c>
+      <c r="G11" t="s">
+        <v>1382</v>
+      </c>
+      <c r="H11" t="s">
+        <v>1383</v>
+      </c>
+      <c r="I11" t="s">
+        <v>1408</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1417</v>
+      </c>
+      <c r="F12" t="s">
+        <v>1418</v>
+      </c>
+      <c r="G12" t="s">
+        <v>1419</v>
+      </c>
+      <c r="H12" t="s">
+        <v>1420</v>
+      </c>
+      <c r="I12" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F13" t="s">
+        <v>1381</v>
+      </c>
+      <c r="G13" t="s">
+        <v>1382</v>
+      </c>
+      <c r="H13" t="s">
+        <v>1383</v>
+      </c>
+      <c r="I13" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F14" t="s">
+        <v>1381</v>
+      </c>
+      <c r="G14" t="s">
+        <v>1426</v>
+      </c>
+      <c r="H14" t="s">
+        <v>1427</v>
+      </c>
+      <c r="I14" t="s">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F15" t="s">
+        <v>1430</v>
+      </c>
+      <c r="G15" t="s">
+        <v>1431</v>
+      </c>
+      <c r="H15" t="s">
+        <v>1432</v>
+      </c>
+      <c r="I15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82695760-AFB9-9947-BCDE-2196089E5678}">
   <dimension ref="A1:U1038"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -70884,7 +71454,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE462CF6-3A6E-774A-8E43-3D35D2607B6F}">
   <dimension ref="A1:H108"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -73688,7 +74258,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA3BCC54-7A77-6647-90D1-72E613354374}">
   <dimension ref="A1:N62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -74101,114 +74671,366 @@
       <c r="N20" s="3"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>15</v>
+      </c>
+      <c r="B21">
+        <v>193</v>
+      </c>
+      <c r="C21">
+        <v>4.6920080000000004</v>
+      </c>
+      <c r="D21">
+        <v>117.581203</v>
+      </c>
+      <c r="E21">
+        <v>1246</v>
+      </c>
+      <c r="F21" t="s">
+        <v>1444</v>
+      </c>
       <c r="M21" s="4"/>
       <c r="N21" s="3"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>16</v>
+      </c>
+      <c r="B22">
+        <v>193</v>
+      </c>
+      <c r="C22">
+        <v>4.6920080000000004</v>
+      </c>
+      <c r="D22">
+        <v>117.581203</v>
+      </c>
+      <c r="E22">
+        <v>983</v>
+      </c>
+      <c r="F22" t="s">
+        <v>1445</v>
+      </c>
       <c r="M22" s="4"/>
       <c r="N22" s="3"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>17</v>
+      </c>
+      <c r="B23">
+        <v>193</v>
+      </c>
+      <c r="C23">
+        <v>4.6920080000000004</v>
+      </c>
+      <c r="D23">
+        <v>117.581203</v>
+      </c>
+      <c r="E23">
+        <v>719</v>
+      </c>
+      <c r="F23" t="s">
+        <v>1446</v>
+      </c>
       <c r="M23" s="4"/>
       <c r="N23" s="3"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>18</v>
+      </c>
+      <c r="B24">
+        <v>193</v>
+      </c>
+      <c r="C24">
+        <v>4.6920080000000004</v>
+      </c>
+      <c r="D24">
+        <v>117.581203</v>
+      </c>
+      <c r="E24">
+        <v>455</v>
+      </c>
+      <c r="F24" t="s">
+        <v>1447</v>
+      </c>
       <c r="M24" s="4"/>
       <c r="N24" s="3"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>19</v>
+      </c>
+      <c r="B25">
+        <v>193</v>
+      </c>
+      <c r="C25">
+        <v>4.6920080000000004</v>
+      </c>
+      <c r="D25">
+        <v>117.581203</v>
+      </c>
+      <c r="E25">
+        <v>191</v>
+      </c>
+      <c r="F25" t="s">
+        <v>1448</v>
+      </c>
       <c r="M25" s="4"/>
       <c r="N25" s="3"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>20</v>
+      </c>
+      <c r="B26">
+        <v>193</v>
+      </c>
+      <c r="C26">
+        <v>4.6920080000000004</v>
+      </c>
+      <c r="D26">
+        <v>117.581203</v>
+      </c>
+      <c r="E26">
+        <v>72</v>
+      </c>
+      <c r="F26" t="s">
+        <v>1449</v>
+      </c>
       <c r="M26" s="4"/>
       <c r="N26" s="3"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>21</v>
+      </c>
+      <c r="B27">
+        <v>193</v>
+      </c>
+      <c r="C27">
+        <v>4.6920080000000004</v>
+      </c>
+      <c r="D27">
+        <v>117.581203</v>
+      </c>
+      <c r="E27">
+        <v>307</v>
+      </c>
+      <c r="F27" t="s">
+        <v>1450</v>
+      </c>
       <c r="M27" s="4"/>
       <c r="N27" s="3"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>22</v>
+      </c>
+      <c r="B28">
+        <v>193</v>
+      </c>
+      <c r="C28">
+        <v>4.6920080000000004</v>
+      </c>
+      <c r="D28">
+        <v>117.581203</v>
+      </c>
+      <c r="E28">
+        <v>569</v>
+      </c>
+      <c r="F28" t="s">
+        <v>1451</v>
+      </c>
       <c r="M28" s="4"/>
       <c r="N28" s="3"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>23</v>
+      </c>
+      <c r="B29">
+        <v>193</v>
+      </c>
+      <c r="C29">
+        <v>4.6920080000000004</v>
+      </c>
+      <c r="D29">
+        <v>117.581203</v>
+      </c>
+      <c r="E29">
+        <v>831</v>
+      </c>
+      <c r="F29" t="s">
+        <v>1452</v>
+      </c>
       <c r="M29" s="4"/>
       <c r="N29" s="3"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>24</v>
+      </c>
+      <c r="B30">
+        <v>193</v>
+      </c>
+      <c r="C30">
+        <v>4.6920080000000004</v>
+      </c>
+      <c r="D30">
+        <v>117.581203</v>
+      </c>
+      <c r="E30">
+        <v>1093</v>
+      </c>
+      <c r="F30" t="s">
+        <v>1453</v>
+      </c>
       <c r="M30" s="4"/>
       <c r="N30" s="3"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>25</v>
+      </c>
+      <c r="B31">
+        <v>193</v>
+      </c>
+      <c r="C31">
+        <v>4.6920080000000004</v>
+      </c>
+      <c r="D31">
+        <v>117.581203</v>
+      </c>
+      <c r="E31">
+        <v>1354</v>
+      </c>
+      <c r="F31" t="s">
+        <v>1454</v>
+      </c>
       <c r="M31" s="4"/>
       <c r="N31" s="3"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>26</v>
+      </c>
+      <c r="B32">
+        <v>193</v>
+      </c>
+      <c r="C32">
+        <v>4.6920080000000004</v>
+      </c>
+      <c r="D32">
+        <v>117.581203</v>
+      </c>
+      <c r="E32">
+        <v>1616</v>
+      </c>
+      <c r="F32" t="s">
+        <v>1455</v>
+      </c>
       <c r="M32" s="4"/>
       <c r="N32" s="3"/>
     </row>
-    <row r="33" spans="13:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>27</v>
+      </c>
+      <c r="B33">
+        <v>193</v>
+      </c>
+      <c r="C33">
+        <v>4.6920080000000004</v>
+      </c>
+      <c r="D33">
+        <v>117.581203</v>
+      </c>
+      <c r="E33">
+        <v>284</v>
+      </c>
+      <c r="F33" t="s">
+        <v>1456</v>
+      </c>
       <c r="M33" s="4"/>
       <c r="N33" s="3"/>
     </row>
-    <row r="34" spans="13:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>28</v>
+      </c>
+      <c r="B34">
+        <v>193</v>
+      </c>
+      <c r="C34">
+        <v>4.6920080000000004</v>
+      </c>
+      <c r="D34">
+        <v>117.581203</v>
+      </c>
+      <c r="E34">
+        <v>461</v>
+      </c>
+      <c r="F34" t="s">
+        <v>1457</v>
+      </c>
       <c r="M34" s="4"/>
       <c r="N34" s="3"/>
     </row>
-    <row r="35" spans="13:14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="M35" s="4"/>
       <c r="N35" s="3"/>
     </row>
-    <row r="36" spans="13:14" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="M36" s="4"/>
       <c r="N36" s="3"/>
     </row>
-    <row r="37" spans="13:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="M37" s="4"/>
       <c r="N37" s="3"/>
     </row>
-    <row r="38" spans="13:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="M38" s="4"/>
       <c r="N38" s="3"/>
     </row>
-    <row r="39" spans="13:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="M39" s="4"/>
       <c r="N39" s="3"/>
     </row>
-    <row r="40" spans="13:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="M40" s="4"/>
       <c r="N40" s="3"/>
     </row>
-    <row r="41" spans="13:14" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="M41" s="4"/>
       <c r="N41" s="3"/>
     </row>
-    <row r="42" spans="13:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="M42" s="4"/>
       <c r="N42" s="3"/>
     </row>
-    <row r="43" spans="13:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="M43" s="4"/>
       <c r="N43" s="3"/>
     </row>
-    <row r="44" spans="13:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="M44" s="4"/>
       <c r="N44" s="3"/>
     </row>
-    <row r="45" spans="13:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="M45" s="4"/>
       <c r="N45" s="3"/>
     </row>
-    <row r="46" spans="13:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="M46" s="4"/>
       <c r="N46" s="3"/>
     </row>
-    <row r="47" spans="13:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="M47" s="4"/>
       <c r="N47" s="3"/>
     </row>
-    <row r="48" spans="13:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="M48" s="4"/>
       <c r="N48" s="3"/>
     </row>

--- a/test/fixtures/Test_format_good_Seq.xlsx
+++ b/test/fixtures/Test_format_good_Seq.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jc2017/Documents/MyRepos/safedata_validator/test/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741A5BF2-874E-8247-BCAC-7B0C9340356C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C19AD6E-3EAD-F841-AB85-AC00A78FBE3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1060" windowWidth="27860" windowHeight="15840" activeTab="7" xr2:uid="{819B57D8-7F20-471A-9405-EB60A28E68AA}"/>
+    <workbookView xWindow="0" yWindow="1060" windowWidth="27860" windowHeight="15840" xr2:uid="{819B57D8-7F20-471A-9405-EB60A28E68AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="6" r:id="rId1"/>
@@ -4355,9 +4355,6 @@
     <t>Reference database link</t>
   </si>
   <si>
-    <t>https://greengenes2.ucsd.edu</t>
-  </si>
-  <si>
     <t>MoreTaxa</t>
   </si>
   <si>
@@ -4407,6 +4404,9 @@
   </si>
   <si>
     <t>ASV_132</t>
+  </si>
+  <si>
+    <t>https://www.arb-silva.de</t>
   </si>
 </sst>
 </file>
@@ -5078,7 +5078,7 @@
         <v>1434</v>
       </c>
       <c r="C28" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -5089,7 +5089,7 @@
         <v>1436</v>
       </c>
       <c r="C29" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -5100,21 +5100,21 @@
         <v>1438</v>
       </c>
       <c r="C30" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>1439</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>1440</v>
+      <c r="B31" s="5"/>
+      <c r="C31" t="s">
+        <v>1457</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D8" r:id="rId1" xr:uid="{6D635858-507F-FB42-869F-7B19AB4CC72D}"/>
-    <hyperlink ref="B31" r:id="rId2" xr:uid="{0ADC1EA3-96B0-B242-A987-A66576FCBCD7}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6935,7 +6935,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="B2" t="s">
         <v>1370</v>
@@ -6964,7 +6964,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="B3" t="s">
         <v>1370</v>
@@ -6993,7 +6993,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="B4" t="s">
         <v>1370</v>
@@ -7022,7 +7022,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B5" t="s">
         <v>1370</v>
@@ -7051,7 +7051,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="B6" t="s">
         <v>1370</v>
@@ -7080,7 +7080,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="B7" t="s">
         <v>1370</v>
@@ -7109,7 +7109,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="B8" t="s">
         <v>1370</v>
@@ -7138,7 +7138,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="B9" t="s">
         <v>1370</v>
@@ -7167,7 +7167,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="B10" t="s">
         <v>1370</v>
@@ -7196,7 +7196,7 @@
     </row>
     <row r="11" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="B11" t="s">
         <v>1370</v>
@@ -7228,7 +7228,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B12" t="s">
         <v>1370</v>
@@ -7257,7 +7257,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="B13" t="s">
         <v>1370</v>
@@ -7286,7 +7286,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="B14" t="s">
         <v>1370</v>
@@ -7315,7 +7315,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="B15" t="s">
         <v>1370</v>
@@ -74687,7 +74687,7 @@
         <v>1246</v>
       </c>
       <c r="F21" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="M21" s="4"/>
       <c r="N21" s="3"/>
@@ -74709,7 +74709,7 @@
         <v>983</v>
       </c>
       <c r="F22" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="M22" s="4"/>
       <c r="N22" s="3"/>
@@ -74731,7 +74731,7 @@
         <v>719</v>
       </c>
       <c r="F23" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="M23" s="4"/>
       <c r="N23" s="3"/>
@@ -74753,7 +74753,7 @@
         <v>455</v>
       </c>
       <c r="F24" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="M24" s="4"/>
       <c r="N24" s="3"/>
@@ -74775,7 +74775,7 @@
         <v>191</v>
       </c>
       <c r="F25" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="M25" s="4"/>
       <c r="N25" s="3"/>
@@ -74797,7 +74797,7 @@
         <v>72</v>
       </c>
       <c r="F26" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="M26" s="4"/>
       <c r="N26" s="3"/>
@@ -74819,7 +74819,7 @@
         <v>307</v>
       </c>
       <c r="F27" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="M27" s="4"/>
       <c r="N27" s="3"/>
@@ -74841,7 +74841,7 @@
         <v>569</v>
       </c>
       <c r="F28" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="M28" s="4"/>
       <c r="N28" s="3"/>
@@ -74863,7 +74863,7 @@
         <v>831</v>
       </c>
       <c r="F29" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="M29" s="4"/>
       <c r="N29" s="3"/>
@@ -74885,7 +74885,7 @@
         <v>1093</v>
       </c>
       <c r="F30" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="M30" s="4"/>
       <c r="N30" s="3"/>
@@ -74907,7 +74907,7 @@
         <v>1354</v>
       </c>
       <c r="F31" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="M31" s="4"/>
       <c r="N31" s="3"/>
@@ -74929,7 +74929,7 @@
         <v>1616</v>
       </c>
       <c r="F32" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="M32" s="4"/>
       <c r="N32" s="3"/>
@@ -74951,7 +74951,7 @@
         <v>284</v>
       </c>
       <c r="F33" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="M33" s="4"/>
       <c r="N33" s="3"/>
@@ -74973,7 +74973,7 @@
         <v>461</v>
       </c>
       <c r="F34" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="M34" s="4"/>
       <c r="N34" s="3"/>

--- a/test/fixtures/Test_format_good_Seq.xlsx
+++ b/test/fixtures/Test_format_good_Seq.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jc2017/Documents/MyRepos/safedata_validator/test/fixtures/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jc2017/Repositories/safedata_validator/test/fixtures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C19AD6E-3EAD-F841-AB85-AC00A78FBE3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECDDD9A6-A806-C947-AD26-EDB27E1EFE18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1060" windowWidth="27860" windowHeight="15840" xr2:uid="{819B57D8-7F20-471A-9405-EB60A28E68AA}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8319" uniqueCount="1458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8318" uniqueCount="1457">
   <si>
     <t>Kingdom</t>
   </si>
@@ -4404,9 +4404,6 @@
   </si>
   <si>
     <t>ASV_132</t>
-  </si>
-  <si>
-    <t>https://www.arb-silva.de</t>
   </si>
 </sst>
 </file>
@@ -5108,9 +5105,6 @@
         <v>1439</v>
       </c>
       <c r="B31" s="5"/>
-      <c r="C31" t="s">
-        <v>1457</v>
-      </c>
     </row>
   </sheetData>
   <hyperlinks>
